--- a/VerveStacks_IND_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3879746-8451-4E83-BCE2-DE161CD507BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8451B839-5280-43FA-AA58-34C80DC01308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E59C84AD-0F90-4CD6-A887-7988C10DF7B7}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{0B6AC798-FAC1-4FD5-A713-4BB4DD1117F0}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -71,130 +71,130 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>e_w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>g_w1143180503-765_IND-w369866141-765_IND</t>
+    <t>e_Bhuj_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>g_Bhuj_IND-Vadodara_IND</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>g_w1143180503-765_IND-w372701897-765_IND</t>
-  </si>
-  <si>
-    <t>e_w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>e_w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>g_w201845280-765_IND-w209826798-765_IND</t>
-  </si>
-  <si>
-    <t>e_w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>g_w201845280-765_IND-w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>e_w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>g_w201845280-765_IND-w353914865-765_IND</t>
-  </si>
-  <si>
-    <t>e_w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>g_w201845280-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_w203673991-400_IND</t>
-  </si>
-  <si>
-    <t>e_w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>g_w203673991-400_IND-w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>e_w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>g_w209826798-765_IND-w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>g_w209826798-765_IND-w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>g_w209826798-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>g_w293597835-765_IND-w315823978-765_IND</t>
-  </si>
-  <si>
-    <t>g_w311118424-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>e_IN684-765_IND</t>
-  </si>
-  <si>
-    <t>g_w315823978-765_IND-IN684-765_IND</t>
-  </si>
-  <si>
-    <t>g_w315823978-765_IND-w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>e_w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>g_w315823978-765_IND-w386153973-765_IND</t>
-  </si>
-  <si>
-    <t>g_w331275940-765_IND-w201845280-765_IND</t>
-  </si>
-  <si>
-    <t>g_w353914865-765_IND-IN684-765_IND</t>
-  </si>
-  <si>
-    <t>g_w353914865-765_IND-w311118424-765_IND</t>
-  </si>
-  <si>
-    <t>g_w353914865-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>g_w372701897-765_IND-w420797421-765_IND</t>
-  </si>
-  <si>
-    <t>g_w386153973-765_IND-w293597835-765_IND</t>
-  </si>
-  <si>
-    <t>g_w420797421-765_IND-w1143180503-765_IND</t>
-  </si>
-  <si>
-    <t>g_w420797421-765_IND-w369866141-765_IND</t>
-  </si>
-  <si>
-    <t>e_w688672711-765_IND</t>
-  </si>
-  <si>
-    <t>g_w688672711-765_IND-w331275940-765_IND</t>
-  </si>
-  <si>
-    <t>e_w759521252-765_IND</t>
-  </si>
-  <si>
-    <t>g_w759521252-765_IND-w311118424-765_IND</t>
+    <t>e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>g_Dharmapuri_IND-Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>g_Fatehpur_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>g_Indore_IND-Jaipur_IND</t>
+  </si>
+  <si>
+    <t>g_Indore_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>g_Indore_IND-Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND</t>
+  </si>
+  <si>
+    <t>g_Korba_IND-Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>g_Korba_IND-Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>g_Korba_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>g_Kurnool_IND-Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>g_Kurnool_IND-Rajahmundry_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>g_Kurnool_IND-Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Medinipur_IND</t>
+  </si>
+  <si>
+    <t>g_Medinipur_IND-Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND</t>
+  </si>
+  <si>
+    <t>g_Moga_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>g_Phalodi_IND-Jaipur_IND</t>
+  </si>
+  <si>
+    <t>g_Phalodi_IND-Moga_IND</t>
+  </si>
+  <si>
+    <t>g_Sikandarabad_IND-Jaipur_IND</t>
+  </si>
+  <si>
+    <t>g_Sikandarabad_IND-Phalodi_IND</t>
+  </si>
+  <si>
+    <t>g_Solapur_IND-Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>g_Tezpur_IND-Fatehpur_IND</t>
+  </si>
+  <si>
+    <t>g_Vadodara_IND-Wardha_IND</t>
+  </si>
+  <si>
+    <t>g_Wardha_IND-Indore_IND</t>
+  </si>
+  <si>
+    <t>g_Wardha_IND-Korba_IND</t>
+  </si>
+  <si>
+    <t>g_Wardha_IND-Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>g_Wardha_IND-Solapur_IND</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -206,79 +206,79 @@
     <t>description</t>
   </si>
   <si>
+    <t>grid link -272.0 km- way/331275940-765;way/688672711-765</t>
+  </si>
+  <si>
+    <t>grid link -345.0 km- way/293597835-765;way/386153973-765</t>
+  </si>
+  <si>
+    <t>grid link -281.0 km- way/311118424-765;way/420797421-765</t>
+  </si>
+  <si>
+    <t>grid link -217.0 km- way/209826798-765;way/369866141-765</t>
+  </si>
+  <si>
+    <t>grid link -266.0 km- way/209826798-765;way/420797421-765</t>
+  </si>
+  <si>
+    <t>grid link -277.0 km- way/209826798-765;way/331275940-765</t>
+  </si>
+  <si>
+    <t>grid link -345.0 km- way/311118424-765;way/353914865-765</t>
+  </si>
+  <si>
+    <t>grid link -387.0 km- IN684-765;way/353914865-765</t>
+  </si>
+  <si>
+    <t>grid link -312.0 km- way/353914865-765;way/420797421-765</t>
+  </si>
+  <si>
+    <t>grid link -169.0 km- way/315823978-765;way/386153973-765</t>
+  </si>
+  <si>
+    <t>grid link -287.0 km- IN684-765;way/315823978-765</t>
+  </si>
+  <si>
+    <t>grid link -309.0 km- way/201845280-765;way/315823978-765</t>
+  </si>
+  <si>
+    <t>grid link -247.0 km- way/311118424-765;way/759521252-765</t>
+  </si>
+  <si>
+    <t>grid link -258.0 km- way/372701897-765;way/420797421-765</t>
+  </si>
+  <si>
     <t>grid link -323.0 km- way/1143180503-765;way/369866141-765</t>
   </si>
   <si>
     <t>grid link -393.0 km- way/1143180503-765;way/372701897-765</t>
   </si>
   <si>
+    <t>grid link -173.0 km- way/369866141-765;way/420797421-765</t>
+  </si>
+  <si>
+    <t>grid link -240.0 km- way/1143180503-765;way/420797421-765</t>
+  </si>
+  <si>
+    <t>grid link -181.0 km- way/293597835-765;way/315823978-765</t>
+  </si>
+  <si>
+    <t>grid link -222.0 km- way/203673991-400;way/311118424-765</t>
+  </si>
+  <si>
+    <t>grid link -257.0 km- way/201845280-765;way/331275940-765</t>
+  </si>
+  <si>
     <t>grid link -212.0 km- way/201845280-765;way/209826798-765</t>
   </si>
   <si>
+    <t>grid link -355.0 km- way/201845280-765;way/353914865-765</t>
+  </si>
+  <si>
+    <t>grid link -320.0 km- way/201845280-765;way/420797421-765</t>
+  </si>
+  <si>
     <t>grid link -394.0 km- way/201845280-765;way/293597835-765</t>
-  </si>
-  <si>
-    <t>grid link -355.0 km- way/201845280-765;way/353914865-765</t>
-  </si>
-  <si>
-    <t>grid link -320.0 km- way/201845280-765;way/420797421-765</t>
-  </si>
-  <si>
-    <t>grid link -222.0 km- way/203673991-400;way/311118424-765</t>
-  </si>
-  <si>
-    <t>grid link -277.0 km- way/209826798-765;way/331275940-765</t>
-  </si>
-  <si>
-    <t>grid link -217.0 km- way/209826798-765;way/369866141-765</t>
-  </si>
-  <si>
-    <t>grid link -266.0 km- way/209826798-765;way/420797421-765</t>
-  </si>
-  <si>
-    <t>grid link -181.0 km- way/293597835-765;way/315823978-765</t>
-  </si>
-  <si>
-    <t>grid link -281.0 km- way/311118424-765;way/420797421-765</t>
-  </si>
-  <si>
-    <t>grid link -287.0 km- IN684-765;way/315823978-765</t>
-  </si>
-  <si>
-    <t>grid link -309.0 km- way/201845280-765;way/315823978-765</t>
-  </si>
-  <si>
-    <t>grid link -169.0 km- way/315823978-765;way/386153973-765</t>
-  </si>
-  <si>
-    <t>grid link -257.0 km- way/201845280-765;way/331275940-765</t>
-  </si>
-  <si>
-    <t>grid link -387.0 km- IN684-765;way/353914865-765</t>
-  </si>
-  <si>
-    <t>grid link -345.0 km- way/311118424-765;way/353914865-765</t>
-  </si>
-  <si>
-    <t>grid link -312.0 km- way/353914865-765;way/420797421-765</t>
-  </si>
-  <si>
-    <t>grid link -258.0 km- way/372701897-765;way/420797421-765</t>
-  </si>
-  <si>
-    <t>grid link -345.0 km- way/293597835-765;way/386153973-765</t>
-  </si>
-  <si>
-    <t>grid link -240.0 km- way/1143180503-765;way/420797421-765</t>
-  </si>
-  <si>
-    <t>grid link -173.0 km- way/369866141-765;way/420797421-765</t>
-  </si>
-  <si>
-    <t>grid link -272.0 km- way/331275940-765;way/688672711-765</t>
-  </si>
-  <si>
-    <t>grid link -247.0 km- way/311118424-765;way/759521252-765</t>
   </si>
   <si>
     <t>~commodity_geo</t>
@@ -1171,7 +1171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0455C0-FD40-4CB6-AE5D-361F66795AC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB62CD7-D2A2-43C2-A3BF-E4D8704FABB3}">
   <dimension ref="B3:R189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1256,16 +1256,16 @@
         <v>55</v>
       </c>
       <c r="O5" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="P5" t="s">
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>81.895088599999994</v>
+        <v>69.592576853385523</v>
       </c>
       <c r="R5">
-        <v>17.15979717252354</v>
+        <v>23.452485058949303</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
@@ -1279,34 +1279,34 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L6" t="s">
         <v>56</v>
       </c>
       <c r="O6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P6" t="s">
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>72.481935936664442</v>
+        <v>78.030826414577206</v>
       </c>
       <c r="R6">
-        <v>27.5115253825116</v>
+        <v>12.133113559842871</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
@@ -1320,34 +1320,34 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s">
         <v>57</v>
       </c>
       <c r="O7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P7" t="s">
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>78.492722981662908</v>
+        <v>80.853483649853217</v>
       </c>
       <c r="R7">
-        <v>20.669102672493342</v>
+        <v>25.957447383134458</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
@@ -1361,34 +1361,34 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L8" t="s">
         <v>58</v>
       </c>
       <c r="O8" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P8" t="s">
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>92.769229427644319</v>
+        <v>75.90401276433046</v>
       </c>
       <c r="R8">
-        <v>26.874103883267651</v>
+        <v>22.908338070793363</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
@@ -1402,34 +1402,34 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" t="s">
         <v>13</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L9" t="s">
         <v>59</v>
       </c>
       <c r="O9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P9" t="s">
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>75.90401276433046</v>
+        <v>75.665218786562164</v>
       </c>
       <c r="R9">
-        <v>22.908338070793363</v>
+        <v>26.651351516019087</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
@@ -1443,10 +1443,10 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -1461,16 +1461,16 @@
         <v>60</v>
       </c>
       <c r="O10" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P10" t="s">
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>76.051201531523105</v>
+        <v>82.762172184031854</v>
       </c>
       <c r="R10">
-        <v>17.607760270934016</v>
+        <v>22.271692751270525</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
@@ -1487,31 +1487,31 @@
         <v>25</v>
       </c>
       <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
         <v>26</v>
-      </c>
-      <c r="G11" t="s">
-        <v>27</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
         <v>61</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P11" t="s">
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>80.853483649853217</v>
+        <v>78.177770343689502</v>
       </c>
       <c r="R11">
-        <v>25.957447383134458</v>
+        <v>15.673490343021944</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
@@ -1525,34 +1525,34 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" t="s">
         <v>28</v>
-      </c>
-      <c r="G12" t="s">
-        <v>29</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
       </c>
       <c r="K12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L12" t="s">
         <v>62</v>
       </c>
       <c r="O12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P12" t="s">
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>78.177770343689502</v>
+        <v>87.379967135716399</v>
       </c>
       <c r="R12">
-        <v>15.673490343021944</v>
+        <v>22.690868695213929</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
@@ -1566,34 +1566,34 @@
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L13" t="s">
         <v>63</v>
       </c>
       <c r="O13" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P13" t="s">
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>73.377135632267908</v>
+        <v>75.146078508432495</v>
       </c>
       <c r="R13">
-        <v>22.317293030637487</v>
+        <v>30.784075715982738</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
@@ -1607,10 +1607,10 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s">
         <v>31</v>
@@ -1625,16 +1625,16 @@
         <v>64</v>
       </c>
       <c r="O14" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="P14" t="s">
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>82.762172184031854</v>
+        <v>72.481935936664442</v>
       </c>
       <c r="R14">
-        <v>22.271692751270525</v>
+        <v>27.5115253825116</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
@@ -1648,34 +1648,34 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" t="s">
         <v>32</v>
-      </c>
-      <c r="G15" t="s">
-        <v>33</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L15" t="s">
         <v>65</v>
       </c>
       <c r="O15" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="P15" t="s">
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>75.665218786562164</v>
+        <v>81.895088599999994</v>
       </c>
       <c r="R15">
-        <v>26.651351516019087</v>
+        <v>17.15979717252354</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
@@ -1689,10 +1689,10 @@
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
         <v>34</v>
@@ -1707,16 +1707,16 @@
         <v>66</v>
       </c>
       <c r="O16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P16" t="s">
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>75.146078508432495</v>
+        <v>77.697852005819513</v>
       </c>
       <c r="R16">
-        <v>30.784075715982738</v>
+        <v>28.196007553336685</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
@@ -1730,10 +1730,10 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
         <v>36</v>
@@ -1748,16 +1748,16 @@
         <v>67</v>
       </c>
       <c r="O17" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="P17" t="s">
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>78.030826414577206</v>
+        <v>76.051201531523105</v>
       </c>
       <c r="R17">
-        <v>12.133113559842871</v>
+        <v>17.607760270934016</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
@@ -1771,34 +1771,34 @@
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
       </c>
       <c r="K18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L18" t="s">
         <v>68</v>
       </c>
       <c r="O18" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="P18" t="s">
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>77.697852005819513</v>
+        <v>92.769229427644319</v>
       </c>
       <c r="R18">
-        <v>28.196007553336685</v>
+        <v>26.874103883267651</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
@@ -1812,34 +1812,34 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
       </c>
       <c r="K19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L19" t="s">
         <v>69</v>
       </c>
       <c r="O19" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="P19" t="s">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>69.592576853385523</v>
+        <v>73.377135632267908</v>
       </c>
       <c r="R19">
-        <v>23.452485058949303</v>
+        <v>22.317293030637487</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
@@ -1853,34 +1853,34 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
       </c>
       <c r="K20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L20" t="s">
         <v>70</v>
       </c>
       <c r="O20" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="P20" t="s">
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>87.379967135716399</v>
+        <v>78.492722981662908</v>
       </c>
       <c r="R20">
-        <v>22.690868695213929</v>
+        <v>20.669102672493342</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
@@ -1894,19 +1894,19 @@
         <v>9</v>
       </c>
       <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
         <v>21</v>
       </c>
-      <c r="F21" t="s">
-        <v>35</v>
-      </c>
       <c r="G21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
       <c r="K21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L21" t="s">
         <v>71</v>
@@ -1935,19 +1935,19 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
       <c r="K22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L22" t="s">
         <v>72</v>
@@ -1976,19 +1976,19 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L23" t="s">
         <v>73</v>
@@ -2017,19 +2017,19 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
       </c>
       <c r="K24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L24" t="s">
         <v>74</v>
@@ -2058,19 +2058,19 @@
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L25" t="s">
         <v>75</v>
@@ -2099,19 +2099,19 @@
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
       </c>
       <c r="K26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L26" t="s">
         <v>76</v>
@@ -2140,19 +2140,19 @@
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
       </c>
       <c r="K27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L27" t="s">
         <v>77</v>
@@ -2181,19 +2181,19 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L28" t="s">
         <v>78</v>
@@ -2222,10 +2222,10 @@
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G29" t="s">
         <v>51</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8451B839-5280-43FA-AA58-34C80DC01308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C368406-2FBE-4A24-A280-D42859484BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{0B6AC798-FAC1-4FD5-A713-4BB4DD1117F0}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{EBA91681-9D47-4496-AD1A-9AC34EF11053}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1171,7 +1171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB62CD7-D2A2-43C2-A3BF-E4D8704FABB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076AF46B-E29A-44CE-A9B4-50B08153BBFA}">
   <dimension ref="B3:R189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1262,10 +1262,10 @@
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>69.592576853385523</v>
+        <v>69.59257685</v>
       </c>
       <c r="R5">
-        <v>23.452485058949303</v>
+        <v>23.452485060000001</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
@@ -1303,10 +1303,10 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>78.030826414577206</v>
+        <v>78.030826410000003</v>
       </c>
       <c r="R6">
-        <v>12.133113559842871</v>
+        <v>12.13311356</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
@@ -1344,10 +1344,10 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>80.853483649853217</v>
+        <v>80.853483650000001</v>
       </c>
       <c r="R7">
-        <v>25.957447383134458</v>
+        <v>25.957447380000001</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
@@ -1385,10 +1385,10 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>75.90401276433046</v>
+        <v>75.904012760000001</v>
       </c>
       <c r="R8">
-        <v>22.908338070793363</v>
+        <v>22.908338069999999</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
@@ -1426,10 +1426,10 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>75.665218786562164</v>
+        <v>75.665218789999997</v>
       </c>
       <c r="R9">
-        <v>26.651351516019087</v>
+        <v>26.651351519999999</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
@@ -1467,10 +1467,10 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>82.762172184031854</v>
+        <v>82.762172179999993</v>
       </c>
       <c r="R10">
-        <v>22.271692751270525</v>
+        <v>22.27169275</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
@@ -1508,10 +1508,10 @@
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>78.177770343689502</v>
+        <v>78.177770339999995</v>
       </c>
       <c r="R11">
-        <v>15.673490343021944</v>
+        <v>15.673490340000001</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
@@ -1549,10 +1549,10 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>87.379967135716399</v>
+        <v>87.379967140000005</v>
       </c>
       <c r="R12">
-        <v>22.690868695213929</v>
+        <v>22.690868699999999</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
@@ -1590,10 +1590,10 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>75.146078508432495</v>
+        <v>75.146078509999995</v>
       </c>
       <c r="R13">
-        <v>30.784075715982738</v>
+        <v>30.784075720000001</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
@@ -1631,10 +1631,10 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>72.481935936664442</v>
+        <v>72.48193594</v>
       </c>
       <c r="R14">
-        <v>27.5115253825116</v>
+        <v>27.511525379999998</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
@@ -1675,7 +1675,7 @@
         <v>81.895088599999994</v>
       </c>
       <c r="R15">
-        <v>17.15979717252354</v>
+        <v>17.159797170000001</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
@@ -1713,10 +1713,10 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>77.697852005819513</v>
+        <v>77.697852010000005</v>
       </c>
       <c r="R16">
-        <v>28.196007553336685</v>
+        <v>28.196007550000001</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
@@ -1754,10 +1754,10 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>76.051201531523105</v>
+        <v>76.05120153</v>
       </c>
       <c r="R17">
-        <v>17.607760270934016</v>
+        <v>17.60776027</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
@@ -1795,10 +1795,10 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>92.769229427644319</v>
+        <v>92.769229429999996</v>
       </c>
       <c r="R18">
-        <v>26.874103883267651</v>
+        <v>26.87410388</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
@@ -1836,10 +1836,10 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>73.377135632267908</v>
+        <v>73.377135629999998</v>
       </c>
       <c r="R19">
-        <v>22.317293030637487</v>
+        <v>22.317293029999998</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
@@ -1877,10 +1877,10 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>78.492722981662908</v>
+        <v>78.492722979999996</v>
       </c>
       <c r="R20">
-        <v>20.669102672493342</v>
+        <v>20.669102670000001</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">

--- a/VerveStacks_IND_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C368406-2FBE-4A24-A280-D42859484BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC5631B1-5865-4A50-B987-8E34B0BCD211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{EBA91681-9D47-4496-AD1A-9AC34EF11053}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{84F99CA7-B9F7-49EC-800B-2C0366B549C1}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -1171,7 +1171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{076AF46B-E29A-44CE-A9B4-50B08153BBFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAD35BE-FD5A-4254-844A-94C5A7E3702B}">
   <dimension ref="B3:R189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC5631B1-5865-4A50-B987-8E34B0BCD211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{025F23E1-C2DE-47EC-AB22-6AA45BECCB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{84F99CA7-B9F7-49EC-800B-2C0366B549C1}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{4A5CF12B-661E-4A43-9C27-488976A840DB}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="253">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -798,9 +798,6 @@
   </si>
   <si>
     <t>elc_won_IND_066</t>
-  </si>
-  <si>
-    <t>elc_won_IND_067</t>
   </si>
 </sst>
 </file>
@@ -1171,8 +1168,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAD35BE-FD5A-4254-844A-94C5A7E3702B}">
-  <dimension ref="B3:R189"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB092ABC-3C45-44B7-8789-9D0D30221EF9}">
+  <dimension ref="B3:R188"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
@@ -1262,10 +1259,10 @@
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>69.59257685</v>
+        <v>69.592576853385523</v>
       </c>
       <c r="R5">
-        <v>23.452485060000001</v>
+        <v>23.452485058949303</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
@@ -1303,10 +1300,10 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>78.030826410000003</v>
+        <v>78.030826414577206</v>
       </c>
       <c r="R6">
-        <v>12.13311356</v>
+        <v>12.133113559842871</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
@@ -1344,10 +1341,10 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>80.853483650000001</v>
+        <v>80.853483649853217</v>
       </c>
       <c r="R7">
-        <v>25.957447380000001</v>
+        <v>25.957447383134458</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
@@ -1385,10 +1382,10 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>75.904012760000001</v>
+        <v>75.90401276433046</v>
       </c>
       <c r="R8">
-        <v>22.908338069999999</v>
+        <v>22.908338070793363</v>
       </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
@@ -1426,10 +1423,10 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>75.665218789999997</v>
+        <v>75.665218786562164</v>
       </c>
       <c r="R9">
-        <v>26.651351519999999</v>
+        <v>26.651351516019087</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
@@ -1467,10 +1464,10 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>82.762172179999993</v>
+        <v>82.762172184031854</v>
       </c>
       <c r="R10">
-        <v>22.27169275</v>
+        <v>22.271692751270525</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
@@ -1508,10 +1505,10 @@
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>78.177770339999995</v>
+        <v>78.177770343689502</v>
       </c>
       <c r="R11">
-        <v>15.673490340000001</v>
+        <v>15.673490343021944</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
@@ -1549,10 +1546,10 @@
         <v>8</v>
       </c>
       <c r="Q12">
-        <v>87.379967140000005</v>
+        <v>87.379967135716399</v>
       </c>
       <c r="R12">
-        <v>22.690868699999999</v>
+        <v>22.690868695213929</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
@@ -1590,10 +1587,10 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>75.146078509999995</v>
+        <v>75.146078508432495</v>
       </c>
       <c r="R13">
-        <v>30.784075720000001</v>
+        <v>30.784075715982738</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
@@ -1631,10 +1628,10 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>72.48193594</v>
+        <v>72.481935936664442</v>
       </c>
       <c r="R14">
-        <v>27.511525379999998</v>
+        <v>27.5115253825116</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
@@ -1675,7 +1672,7 @@
         <v>81.895088599999994</v>
       </c>
       <c r="R15">
-        <v>17.159797170000001</v>
+        <v>17.15979717252354</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
@@ -1713,10 +1710,10 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>77.697852010000005</v>
+        <v>77.697852005819513</v>
       </c>
       <c r="R16">
-        <v>28.196007550000001</v>
+        <v>28.196007553336685</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
@@ -1754,10 +1751,10 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>76.05120153</v>
+        <v>76.051201531523105</v>
       </c>
       <c r="R17">
-        <v>17.60776027</v>
+        <v>17.607760270934016</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
@@ -1795,10 +1792,10 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>92.769229429999996</v>
+        <v>92.769229427644319</v>
       </c>
       <c r="R18">
-        <v>26.87410388</v>
+        <v>26.874103883267651</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
@@ -1836,10 +1833,10 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>73.377135629999998</v>
+        <v>73.377135632267908</v>
       </c>
       <c r="R19">
-        <v>22.317293029999998</v>
+        <v>22.317293030637487</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
@@ -1877,10 +1874,10 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>78.492722979999996</v>
+        <v>78.492722981662908</v>
       </c>
       <c r="R20">
-        <v>20.669102670000001</v>
+        <v>20.669102672493342</v>
       </c>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
@@ -1918,10 +1915,10 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>72.01530541613829</v>
+        <v>95.162232610422222</v>
       </c>
       <c r="R21">
-        <v>23.940177048687382</v>
+        <v>27.893720802676519</v>
       </c>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
@@ -1959,10 +1956,10 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>72.323497564065292</v>
+        <v>95.678904356646044</v>
       </c>
       <c r="R22">
-        <v>25.762589391573918</v>
+        <v>27.616837641447088</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
@@ -2000,10 +1997,10 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>74.92863083024271</v>
+        <v>94.597756225167842</v>
       </c>
       <c r="R23">
-        <v>25.215717246195734</v>
+        <v>27.109313934866226</v>
       </c>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
@@ -2041,10 +2038,10 @@
         <v>8</v>
       </c>
       <c r="Q24">
-        <v>71.979982922841245</v>
+        <v>92.084380653014193</v>
       </c>
       <c r="R24">
-        <v>22.089771430079018</v>
+        <v>26.973082364209532</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
@@ -2082,10 +2079,10 @@
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>73.75439597012047</v>
+        <v>90.580571695618644</v>
       </c>
       <c r="R25">
-        <v>23.401710039230601</v>
+        <v>25.331244673876583</v>
       </c>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
@@ -2123,10 +2120,10 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>73.203935226300871</v>
+        <v>90.088813711116686</v>
       </c>
       <c r="R26">
-        <v>19.571868623472721</v>
+        <v>26.347320792040019</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
@@ -2164,10 +2161,10 @@
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>74.655550178307777</v>
+        <v>92.546702607694158</v>
       </c>
       <c r="R27">
-        <v>20.973992616098737</v>
+        <v>22.65193104025149</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
@@ -2205,10 +2202,10 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>78.132581760570787</v>
+        <v>91.654903285132121</v>
       </c>
       <c r="R28">
-        <v>21.298615212019719</v>
+        <v>23.777133025144924</v>
       </c>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
@@ -2246,10 +2243,10 @@
         <v>8</v>
       </c>
       <c r="Q29">
-        <v>76.329011042015125</v>
+        <v>92.986095851336842</v>
       </c>
       <c r="R29">
-        <v>20.763554465432239</v>
+        <v>26.335074800055896</v>
       </c>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
@@ -2260,10 +2257,10 @@
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>75.739329326526175</v>
+        <v>94.269460528249525</v>
       </c>
       <c r="R30">
-        <v>23.23600900338716</v>
+        <v>25.924881972559486</v>
       </c>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.25">
@@ -2274,10 +2271,10 @@
         <v>8</v>
       </c>
       <c r="Q31">
-        <v>77.538069578828527</v>
+        <v>92.445894855815595</v>
       </c>
       <c r="R31">
-        <v>23.441086592996527</v>
+        <v>24.796283713760488</v>
       </c>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
@@ -2288,10 +2285,10 @@
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>73.848509064471259</v>
+        <v>94.345871649004167</v>
       </c>
       <c r="R32">
-        <v>29.451941382432882</v>
+        <v>24.450646852147571</v>
       </c>
     </row>
     <row r="33" spans="15:18" x14ac:dyDescent="0.25">
@@ -2302,10 +2299,10 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>74.994352434716205</v>
+        <v>80.606617981443563</v>
       </c>
       <c r="R33">
-        <v>30.889610466578063</v>
+        <v>24.31722425770889</v>
       </c>
     </row>
     <row r="34" spans="15:18" x14ac:dyDescent="0.25">
@@ -2316,10 +2313,10 @@
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>72.130555374386333</v>
+        <v>81.958507480329203</v>
       </c>
       <c r="R34">
-        <v>27.782553394318072</v>
+        <v>27.55951580673932</v>
       </c>
     </row>
     <row r="35" spans="15:18" x14ac:dyDescent="0.25">
@@ -2330,10 +2327,10 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>74.792171203407761</v>
+        <v>79.699115070602147</v>
       </c>
       <c r="R35">
-        <v>27.999653865710783</v>
+        <v>26.383501441796746</v>
       </c>
     </row>
     <row r="36" spans="15:18" x14ac:dyDescent="0.25">
@@ -2344,10 +2341,10 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>75.328108254891234</v>
+        <v>81.513212233838857</v>
       </c>
       <c r="R36">
-        <v>32.369004546556781</v>
+        <v>25.961441796472709</v>
       </c>
     </row>
     <row r="37" spans="15:18" x14ac:dyDescent="0.25">
@@ -2358,10 +2355,10 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>77.138454353946159</v>
+        <v>84.428490924191877</v>
       </c>
       <c r="R37">
-        <v>30.078269892451456</v>
+        <v>26.525927540081284</v>
       </c>
     </row>
     <row r="38" spans="15:18" x14ac:dyDescent="0.25">
@@ -2372,10 +2369,10 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>77.66979989677975</v>
+        <v>83.582913959798233</v>
       </c>
       <c r="R38">
-        <v>25.353800245391959</v>
+        <v>24.521017808688651</v>
       </c>
     </row>
     <row r="39" spans="15:18" x14ac:dyDescent="0.25">
@@ -2386,10 +2383,10 @@
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>79.922674256012414</v>
+        <v>85.020972700910107</v>
       </c>
       <c r="R39">
-        <v>24.69495322947316</v>
+        <v>20.267712814945369</v>
       </c>
     </row>
     <row r="40" spans="15:18" x14ac:dyDescent="0.25">
@@ -2400,10 +2397,10 @@
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>79.723985175188076</v>
+        <v>86.506425397145236</v>
       </c>
       <c r="R40">
-        <v>26.471952337563291</v>
+        <v>21.316843980271184</v>
       </c>
     </row>
     <row r="41" spans="15:18" x14ac:dyDescent="0.25">
@@ -2414,10 +2411,10 @@
         <v>8</v>
       </c>
       <c r="Q41">
-        <v>76.380230155914333</v>
+        <v>83.399512273884866</v>
       </c>
       <c r="R41">
-        <v>26.884841613709771</v>
+        <v>21.043761288625959</v>
       </c>
     </row>
     <row r="42" spans="15:18" x14ac:dyDescent="0.25">
@@ -2428,10 +2425,10 @@
         <v>8</v>
       </c>
       <c r="Q42">
-        <v>77.457861310026132</v>
+        <v>84.691615831874245</v>
       </c>
       <c r="R42">
-        <v>28.171500161202225</v>
+        <v>22.301037494716983</v>
       </c>
     </row>
     <row r="43" spans="15:18" x14ac:dyDescent="0.25">
@@ -2442,10 +2439,10 @@
         <v>8</v>
       </c>
       <c r="Q43">
-        <v>79.647824868329138</v>
+        <v>87.628239095813171</v>
       </c>
       <c r="R43">
-        <v>29.347431056795799</v>
+        <v>26.058253347633784</v>
       </c>
     </row>
     <row r="44" spans="15:18" x14ac:dyDescent="0.25">
@@ -2456,10 +2453,10 @@
         <v>8</v>
       </c>
       <c r="Q44">
-        <v>79.817174165971352</v>
+        <v>88.065380035257064</v>
       </c>
       <c r="R44">
-        <v>28.214905273412281</v>
+        <v>23.631935868013976</v>
       </c>
     </row>
     <row r="45" spans="15:18" x14ac:dyDescent="0.25">
@@ -2470,10 +2467,10 @@
         <v>8</v>
       </c>
       <c r="Q45">
-        <v>84.906854690618076</v>
+        <v>87.744335886089701</v>
       </c>
       <c r="R45">
-        <v>26.542230132073865</v>
+        <v>24.80613255949843</v>
       </c>
     </row>
     <row r="46" spans="15:18" x14ac:dyDescent="0.25">
@@ -2484,10 +2481,10 @@
         <v>8</v>
       </c>
       <c r="Q46">
-        <v>81.909913684164707</v>
+        <v>88.438189470207149</v>
       </c>
       <c r="R46">
-        <v>27.41535306419388</v>
+        <v>22.45842969369151</v>
       </c>
     </row>
     <row r="47" spans="15:18" x14ac:dyDescent="0.25">
@@ -2498,10 +2495,10 @@
         <v>8</v>
       </c>
       <c r="Q47">
-        <v>82.064463522199645</v>
+        <v>86.722505798487134</v>
       </c>
       <c r="R47">
-        <v>24.931943564621783</v>
+        <v>22.927728025420791</v>
       </c>
     </row>
     <row r="48" spans="15:18" x14ac:dyDescent="0.25">
@@ -2512,10 +2509,10 @@
         <v>8</v>
       </c>
       <c r="Q48">
-        <v>83.663810272051307</v>
+        <v>85.735856534484711</v>
       </c>
       <c r="R48">
-        <v>25.570037966723085</v>
+        <v>24.187657520268608</v>
       </c>
     </row>
     <row r="49" spans="15:18" x14ac:dyDescent="0.25">
@@ -2526,10 +2523,10 @@
         <v>8</v>
       </c>
       <c r="Q49">
-        <v>70.209932684848098</v>
+        <v>78.878413559497417</v>
       </c>
       <c r="R49">
-        <v>26.822004333517569</v>
+        <v>10.504393335127451</v>
       </c>
     </row>
     <row r="50" spans="15:18" x14ac:dyDescent="0.25">
@@ -2540,10 +2537,10 @@
         <v>8</v>
       </c>
       <c r="Q50">
-        <v>69.9628674302528</v>
+        <v>77.06767511606877</v>
       </c>
       <c r="R50">
-        <v>23.974943881323178</v>
+        <v>9.137397690734506</v>
       </c>
     </row>
     <row r="51" spans="15:18" x14ac:dyDescent="0.25">
@@ -2554,10 +2551,10 @@
         <v>8</v>
       </c>
       <c r="Q51">
-        <v>70.312870487012432</v>
+        <v>76.558554080404249</v>
       </c>
       <c r="R51">
-        <v>22.031083021744013</v>
+        <v>11.226969498165088</v>
       </c>
     </row>
     <row r="52" spans="15:18" x14ac:dyDescent="0.25">
@@ -2568,10 +2565,10 @@
         <v>8</v>
       </c>
       <c r="Q52">
-        <v>87.63284952501175</v>
+        <v>78.030451964254922</v>
       </c>
       <c r="R52">
-        <v>22.183640582672592</v>
+        <v>11.507621226853775</v>
       </c>
     </row>
     <row r="53" spans="15:18" x14ac:dyDescent="0.25">
@@ -2582,10 +2579,10 @@
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>87.799415974822153</v>
+        <v>83.515249081931756</v>
       </c>
       <c r="R53">
-        <v>25.988701451121266</v>
+        <v>18.297166863653832</v>
       </c>
     </row>
     <row r="54" spans="15:18" x14ac:dyDescent="0.25">
@@ -2596,10 +2593,10 @@
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>87.749394240479006</v>
+        <v>80.766065933161698</v>
       </c>
       <c r="R54">
-        <v>24.75124696562656</v>
+        <v>16.746787868199885</v>
       </c>
     </row>
     <row r="55" spans="15:18" x14ac:dyDescent="0.25">
@@ -2610,10 +2607,10 @@
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>87.503087921397949</v>
+        <v>77.592607797183973</v>
       </c>
       <c r="R55">
-        <v>23.593158281395816</v>
+        <v>16.717737568197382</v>
       </c>
     </row>
     <row r="56" spans="15:18" x14ac:dyDescent="0.25">
@@ -2624,10 +2621,10 @@
         <v>8</v>
       </c>
       <c r="Q56">
-        <v>94.345871649004167</v>
+        <v>78.53671045262692</v>
       </c>
       <c r="R56">
-        <v>24.450646852147571</v>
+        <v>15.655512883330466</v>
       </c>
     </row>
     <row r="57" spans="15:18" x14ac:dyDescent="0.25">
@@ -2638,10 +2635,10 @@
         <v>8</v>
       </c>
       <c r="Q57">
-        <v>94.275813463711927</v>
+        <v>79.600537241704529</v>
       </c>
       <c r="R57">
-        <v>25.932079217995447</v>
+        <v>12.695725765835803</v>
       </c>
     </row>
     <row r="58" spans="15:18" x14ac:dyDescent="0.25">
@@ -2652,10 +2649,10 @@
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>92.647721575694646</v>
+        <v>79.645710453009926</v>
       </c>
       <c r="R58">
-        <v>25.370723287781249</v>
+        <v>14.595490354840878</v>
       </c>
     </row>
     <row r="59" spans="15:18" x14ac:dyDescent="0.25">
@@ -2666,10 +2663,10 @@
         <v>8</v>
       </c>
       <c r="Q59">
-        <v>92.547734691435167</v>
+        <v>78.335810324430909</v>
       </c>
       <c r="R59">
-        <v>22.573062394491476</v>
+        <v>13.73915763611522</v>
       </c>
     </row>
     <row r="60" spans="15:18" x14ac:dyDescent="0.25">
@@ -2680,10 +2677,10 @@
         <v>8</v>
       </c>
       <c r="Q60">
-        <v>91.660951031916625</v>
+        <v>74.876957067998788</v>
       </c>
       <c r="R60">
-        <v>23.77438784675067</v>
+        <v>19.119778400148171</v>
       </c>
     </row>
     <row r="61" spans="15:18" x14ac:dyDescent="0.25">
@@ -2694,10 +2691,10 @@
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>93.709478990781804</v>
+        <v>73.5913244181788</v>
       </c>
       <c r="R61">
-        <v>26.855882172919969</v>
+        <v>18.07393392476046</v>
       </c>
     </row>
     <row r="62" spans="15:18" x14ac:dyDescent="0.25">
@@ -2708,10 +2705,10 @@
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>95.65235899806126</v>
+        <v>77.156379009071188</v>
       </c>
       <c r="R62">
-        <v>27.576626654773627</v>
+        <v>18.656031955819039</v>
       </c>
     </row>
     <row r="63" spans="15:18" x14ac:dyDescent="0.25">
@@ -2722,10 +2719,10 @@
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>95.290401439517126</v>
+        <v>75.487933132067681</v>
       </c>
       <c r="R63">
-        <v>27.94126922135878</v>
+        <v>17.568426359523951</v>
       </c>
     </row>
     <row r="64" spans="15:18" x14ac:dyDescent="0.25">
@@ -2736,10 +2733,10 @@
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>90.488191424015938</v>
+        <v>74.542637644301038</v>
       </c>
       <c r="R64">
-        <v>25.715655993691403</v>
+        <v>15.702788983402606</v>
       </c>
     </row>
     <row r="65" spans="15:18" x14ac:dyDescent="0.25">
@@ -2750,10 +2747,10 @@
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>88.899556417890167</v>
+        <v>75.8502505173728</v>
       </c>
       <c r="R65">
-        <v>26.580928877190129</v>
+        <v>15.54304126688014</v>
       </c>
     </row>
     <row r="66" spans="15:18" x14ac:dyDescent="0.25">
@@ -2764,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>90.902380510161123</v>
+        <v>76.682358237502683</v>
       </c>
       <c r="R66">
-        <v>26.58118329802992</v>
+        <v>13.2686602697427</v>
       </c>
     </row>
     <row r="67" spans="15:18" x14ac:dyDescent="0.25">
@@ -2778,10 +2775,10 @@
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>83.874432570520142</v>
+        <v>75.227500296397494</v>
       </c>
       <c r="R67">
-        <v>18.504131255890169</v>
+        <v>13.284216758700872</v>
       </c>
     </row>
     <row r="68" spans="15:18" x14ac:dyDescent="0.25">
@@ -2792,10 +2789,10 @@
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>85.185447365975165</v>
+        <v>79.484349098731869</v>
       </c>
       <c r="R68">
-        <v>20.089138134163729</v>
+        <v>21.853538373607162</v>
       </c>
     </row>
     <row r="69" spans="15:18" x14ac:dyDescent="0.25">
@@ -2806,10 +2803,10 @@
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>80.447788094688121</v>
+        <v>81.738794488667125</v>
       </c>
       <c r="R69">
-        <v>18.857584565270912</v>
+        <v>22.884527788344801</v>
       </c>
     </row>
     <row r="70" spans="15:18" x14ac:dyDescent="0.25">
@@ -2820,10 +2817,10 @@
         <v>8</v>
       </c>
       <c r="Q70">
-        <v>82.131914309855873</v>
+        <v>81.78926268910061</v>
       </c>
       <c r="R70">
-        <v>18.661158935770491</v>
+        <v>21.505424226989053</v>
       </c>
     </row>
     <row r="71" spans="15:18" x14ac:dyDescent="0.25">
@@ -2834,10 +2831,10 @@
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>82.249640216459966</v>
+        <v>82.163640057751238</v>
       </c>
       <c r="R71">
-        <v>19.901684051495504</v>
+        <v>18.616083753584618</v>
       </c>
     </row>
     <row r="72" spans="15:18" x14ac:dyDescent="0.25">
@@ -2848,10 +2845,10 @@
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>80.212365572123872</v>
+        <v>81.480874680905245</v>
       </c>
       <c r="R72">
-        <v>22.705224286477208</v>
+        <v>19.532993714286292</v>
       </c>
     </row>
     <row r="73" spans="15:18" x14ac:dyDescent="0.25">
@@ -2862,10 +2859,10 @@
         <v>8</v>
       </c>
       <c r="Q73">
-        <v>79.947473267587768</v>
+        <v>79.14195624358581</v>
       </c>
       <c r="R73">
-        <v>20.394113196239889</v>
+        <v>19.865313903785481</v>
       </c>
     </row>
     <row r="74" spans="15:18" x14ac:dyDescent="0.25">
@@ -2876,10 +2873,10 @@
         <v>8</v>
       </c>
       <c r="Q74">
-        <v>81.554009768177181</v>
+        <v>79.717592517095639</v>
       </c>
       <c r="R74">
-        <v>21.386323508456584</v>
+        <v>18.192057864555959</v>
       </c>
     </row>
     <row r="75" spans="15:18" x14ac:dyDescent="0.25">
@@ -2890,10 +2887,10 @@
         <v>8</v>
       </c>
       <c r="Q75">
-        <v>83.489328677981362</v>
+        <v>73.964019938268009</v>
       </c>
       <c r="R75">
-        <v>21.45494863014677</v>
+        <v>25.212889640967767</v>
       </c>
     </row>
     <row r="76" spans="15:18" x14ac:dyDescent="0.25">
@@ -2904,10 +2901,10 @@
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>85.583788240668881</v>
+        <v>71.764037802011089</v>
       </c>
       <c r="R76">
-        <v>22.18323596791473</v>
+        <v>21.690024624190663</v>
       </c>
     </row>
     <row r="77" spans="15:18" x14ac:dyDescent="0.25">
@@ -2918,10 +2915,10 @@
         <v>8</v>
       </c>
       <c r="Q77">
-        <v>82.955875010904052</v>
+        <v>71.335782385461201</v>
       </c>
       <c r="R77">
-        <v>23.057557657357972</v>
+        <v>22.939448631127931</v>
       </c>
     </row>
     <row r="78" spans="15:18" x14ac:dyDescent="0.25">
@@ -2932,10 +2929,10 @@
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>85.043593089105116</v>
+        <v>71.914824943781099</v>
       </c>
       <c r="R78">
-        <v>24.189709830493399</v>
+        <v>25.528712199645032</v>
       </c>
     </row>
     <row r="79" spans="15:18" x14ac:dyDescent="0.25">
@@ -2946,10 +2943,10 @@
         <v>8</v>
       </c>
       <c r="Q79">
-        <v>76.927061367471381</v>
+        <v>69.641559139694749</v>
       </c>
       <c r="R79">
-        <v>17.165250319183521</v>
+        <v>23.580064059585681</v>
       </c>
     </row>
     <row r="80" spans="15:18" x14ac:dyDescent="0.25">
@@ -2960,10 +2957,10 @@
         <v>8</v>
       </c>
       <c r="Q80">
-        <v>78.467237584757981</v>
+        <v>76.2529578606689</v>
       </c>
       <c r="R80">
-        <v>18.682280085562315</v>
+        <v>20.220733501265094</v>
       </c>
     </row>
     <row r="81" spans="15:18" x14ac:dyDescent="0.25">
@@ -2974,10 +2971,10 @@
         <v>8</v>
       </c>
       <c r="Q81">
-        <v>77.508765165174864</v>
+        <v>77.468039254618546</v>
       </c>
       <c r="R81">
-        <v>19.636785620416653</v>
+        <v>21.440879518105877</v>
       </c>
     </row>
     <row r="82" spans="15:18" x14ac:dyDescent="0.25">
@@ -2988,10 +2985,10 @@
         <v>8</v>
       </c>
       <c r="Q82">
-        <v>75.003230952348488</v>
+        <v>73.197801279068585</v>
       </c>
       <c r="R82">
-        <v>18.262746739567483</v>
+        <v>20.396478800724161</v>
       </c>
     </row>
     <row r="83" spans="15:18" x14ac:dyDescent="0.25">
@@ -3002,10 +2999,10 @@
         <v>8</v>
       </c>
       <c r="Q83">
-        <v>74.177108940575778</v>
+        <v>74.718501437117752</v>
       </c>
       <c r="R83">
-        <v>15.934631582549706</v>
+        <v>21.259902744576475</v>
       </c>
     </row>
     <row r="84" spans="15:18" x14ac:dyDescent="0.25">
@@ -3016,10 +3013,10 @@
         <v>8</v>
       </c>
       <c r="Q84">
-        <v>75.539380148153072</v>
+        <v>73.988713104139038</v>
       </c>
       <c r="R84">
-        <v>15.564279067442708</v>
+        <v>23.236301590418776</v>
       </c>
     </row>
     <row r="85" spans="15:18" x14ac:dyDescent="0.25">
@@ -3030,10 +3027,10 @@
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>81.594689869695102</v>
+        <v>76.360488664096508</v>
       </c>
       <c r="R85">
-        <v>16.804687119123308</v>
+        <v>23.021647928284843</v>
       </c>
     </row>
     <row r="86" spans="15:18" x14ac:dyDescent="0.25">
@@ -3044,10 +3041,10 @@
         <v>8</v>
       </c>
       <c r="Q86">
-        <v>80.199256007373833</v>
+        <v>78.562314318711572</v>
       </c>
       <c r="R86">
-        <v>17.279361538540549</v>
+        <v>23.844650435637025</v>
       </c>
     </row>
     <row r="87" spans="15:18" x14ac:dyDescent="0.25">
@@ -3058,10 +3055,10 @@
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>78.066053560719922</v>
+        <v>78.027034101805441</v>
       </c>
       <c r="R87">
-        <v>14.083502680353268</v>
+        <v>25.504371809022757</v>
       </c>
     </row>
     <row r="88" spans="15:18" x14ac:dyDescent="0.25">
@@ -3072,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="Q88">
-        <v>78.210973456285771</v>
+        <v>76.434449242765709</v>
       </c>
       <c r="R88">
-        <v>15.863949455046912</v>
+        <v>24.816296140449264</v>
       </c>
     </row>
     <row r="89" spans="15:18" x14ac:dyDescent="0.25">
@@ -3086,10 +3083,10 @@
         <v>8</v>
       </c>
       <c r="Q89">
-        <v>79.339421919695269</v>
+        <v>78.670396495142271</v>
       </c>
       <c r="R89">
-        <v>12.66263811234435</v>
+        <v>29.40190299120264</v>
       </c>
     </row>
     <row r="90" spans="15:18" x14ac:dyDescent="0.25">
@@ -3100,10 +3097,10 @@
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>79.595087805605004</v>
+        <v>79.844150203644304</v>
       </c>
       <c r="R90">
-        <v>14.622153496205565</v>
+        <v>28.385614913322083</v>
       </c>
     </row>
     <row r="91" spans="15:18" x14ac:dyDescent="0.25">
@@ -3114,10 +3111,10 @@
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>78.456689326362721</v>
+        <v>77.628395787297492</v>
       </c>
       <c r="R91">
-        <v>9.2828165306186659</v>
+        <v>27.882415320274731</v>
       </c>
     </row>
     <row r="92" spans="15:18" x14ac:dyDescent="0.25">
@@ -3128,10 +3125,10 @@
         <v>8</v>
       </c>
       <c r="Q92">
-        <v>79.322415400123347</v>
+        <v>76.124134535246441</v>
       </c>
       <c r="R92">
-        <v>10.91886508463346</v>
+        <v>26.651001883724671</v>
       </c>
     </row>
     <row r="93" spans="15:18" x14ac:dyDescent="0.25">
@@ -3142,10 +3139,10 @@
         <v>8</v>
       </c>
       <c r="Q93">
-        <v>78.22469868970876</v>
+        <v>75.322492960532301</v>
       </c>
       <c r="R93">
-        <v>10.694962484380181</v>
+        <v>28.185100700140872</v>
       </c>
     </row>
     <row r="94" spans="15:18" x14ac:dyDescent="0.25">
@@ -3156,10 +3153,10 @@
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>76.157836475227754</v>
+        <v>73.365935679815195</v>
       </c>
       <c r="R94">
-        <v>11.070325439391326</v>
+        <v>28.495583704687725</v>
       </c>
     </row>
     <row r="95" spans="15:18" x14ac:dyDescent="0.25">
@@ -3170,10 +3167,10 @@
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>76.933313582397204</v>
+        <v>70.676366152806125</v>
       </c>
       <c r="R95">
-        <v>9.3619369199647302</v>
+        <v>26.892312386477112</v>
       </c>
     </row>
     <row r="96" spans="15:18" x14ac:dyDescent="0.25">
@@ -3184,10 +3181,10 @@
         <v>8</v>
       </c>
       <c r="Q96">
-        <v>75.118441418466219</v>
+        <v>74.979861298391867</v>
       </c>
       <c r="R96">
-        <v>13.275262016710732</v>
+        <v>30.560929455971198</v>
       </c>
     </row>
     <row r="97" spans="15:18" x14ac:dyDescent="0.25">
@@ -3198,10 +3195,10 @@
         <v>8</v>
       </c>
       <c r="Q97">
-        <v>77.39317984021622</v>
+        <v>75.328108254891234</v>
       </c>
       <c r="R97">
-        <v>12.076302892032931</v>
+        <v>32.369004546556781</v>
       </c>
     </row>
     <row r="98" spans="15:18" x14ac:dyDescent="0.25">
@@ -3212,10 +3209,10 @@
         <v>8</v>
       </c>
       <c r="Q98">
-        <v>76.529851619102828</v>
+        <v>77.086231517473834</v>
       </c>
       <c r="R98">
-        <v>13.183651147633009</v>
+        <v>30.530795340527071</v>
       </c>
     </row>
     <row r="99" spans="15:18" x14ac:dyDescent="0.25">
@@ -3226,10 +3223,10 @@
         <v>8</v>
       </c>
       <c r="Q99">
-        <v>71.842743304758585</v>
+        <v>72.10373153455285</v>
       </c>
       <c r="R99">
-        <v>11.068898099656709</v>
+        <v>12.831190062359031</v>
       </c>
     </row>
     <row r="100" spans="15:18" x14ac:dyDescent="0.25">
@@ -3240,10 +3237,10 @@
         <v>8</v>
       </c>
       <c r="Q100">
-        <v>72.133385027577177</v>
+        <v>73.311612255303388</v>
       </c>
       <c r="R100">
-        <v>12.890615551378485</v>
+        <v>14.517332833443366</v>
       </c>
     </row>
     <row r="101" spans="15:18" x14ac:dyDescent="0.25">
@@ -3254,10 +3251,10 @@
         <v>8</v>
       </c>
       <c r="Q101">
-        <v>73.301161934079801</v>
+        <v>72.547721549064121</v>
       </c>
       <c r="R101">
-        <v>14.500870941812488</v>
+        <v>16.246545066428236</v>
       </c>
     </row>
     <row r="102" spans="15:18" x14ac:dyDescent="0.25">
@@ -3268,10 +3265,10 @@
         <v>8</v>
       </c>
       <c r="Q102">
-        <v>72.383149970196371</v>
+        <v>68.637474643362168</v>
       </c>
       <c r="R102">
-        <v>16.937858360197275</v>
+        <v>21.443683766845677</v>
       </c>
     </row>
     <row r="103" spans="15:18" x14ac:dyDescent="0.25">
@@ -3282,10 +3279,10 @@
         <v>8</v>
       </c>
       <c r="Q103">
-        <v>72.885826415852506</v>
+        <v>67.816370188269687</v>
       </c>
       <c r="R103">
-        <v>15.580799251375479</v>
+        <v>22.459981324731164</v>
       </c>
     </row>
     <row r="104" spans="15:18" x14ac:dyDescent="0.25">
@@ -3296,10 +3293,10 @@
         <v>8</v>
       </c>
       <c r="Q104">
-        <v>67.565303942781298</v>
+        <v>71.476213429601088</v>
       </c>
       <c r="R104">
-        <v>22.564386597052057</v>
+        <v>18.473437408178992</v>
       </c>
     </row>
     <row r="105" spans="15:18" x14ac:dyDescent="0.25">
@@ -3310,10 +3307,10 @@
         <v>8</v>
       </c>
       <c r="Q105">
-        <v>68.369225508640312</v>
+        <v>72.258641968560795</v>
       </c>
       <c r="R105">
-        <v>21.843450436836243</v>
+        <v>17.766068597117588</v>
       </c>
     </row>
     <row r="106" spans="15:18" x14ac:dyDescent="0.25">
@@ -3324,10 +3321,10 @@
         <v>8</v>
       </c>
       <c r="Q106">
-        <v>71.687323687255343</v>
+        <v>70.211779042366572</v>
       </c>
       <c r="R106">
-        <v>18.362408966417828</v>
+        <v>19.725003417896119</v>
       </c>
     </row>
     <row r="107" spans="15:18" x14ac:dyDescent="0.25">
@@ -3338,10 +3335,10 @@
         <v>8</v>
       </c>
       <c r="Q107">
-        <v>69.523978949454545</v>
+        <v>71.468485531282241</v>
       </c>
       <c r="R107">
-        <v>20.563098426100865</v>
+        <v>19.498634613717769</v>
       </c>
     </row>
     <row r="108" spans="15:18" x14ac:dyDescent="0.25">
@@ -3352,10 +3349,10 @@
         <v>8</v>
       </c>
       <c r="Q108">
-        <v>70.489223393236372</v>
+        <v>70.052771659579804</v>
       </c>
       <c r="R108">
-        <v>19.444057687436462</v>
+        <v>20.664319816781006</v>
       </c>
     </row>
     <row r="109" spans="15:18" x14ac:dyDescent="0.25">
@@ -3366,10 +3363,10 @@
         <v>8</v>
       </c>
       <c r="Q109">
-        <v>70.585247722248056</v>
+        <v>88.259977445722924</v>
       </c>
       <c r="R109">
-        <v>20.371266713121692</v>
+        <v>20.466992894954146</v>
       </c>
     </row>
     <row r="110" spans="15:18" x14ac:dyDescent="0.25">
@@ -3380,10 +3377,10 @@
         <v>8</v>
       </c>
       <c r="Q110">
-        <v>71.468485531282241</v>
+        <v>89.249853772557117</v>
       </c>
       <c r="R110">
-        <v>19.498634613717769</v>
+        <v>20.697238047149398</v>
       </c>
     </row>
     <row r="111" spans="15:18" x14ac:dyDescent="0.25">
@@ -3394,10 +3391,10 @@
         <v>8</v>
       </c>
       <c r="Q111">
-        <v>80.504533392317782</v>
+        <v>84.322741673740026</v>
       </c>
       <c r="R111">
-        <v>12.57199809549796</v>
+        <v>18.124069545734084</v>
       </c>
     </row>
     <row r="112" spans="15:18" x14ac:dyDescent="0.25">
@@ -3408,10 +3405,10 @@
         <v>8</v>
       </c>
       <c r="Q112">
-        <v>80.410720845682292</v>
+        <v>87.287671092538389</v>
       </c>
       <c r="R112">
-        <v>10.58438967691929</v>
+        <v>20.209245969976315</v>
       </c>
     </row>
     <row r="113" spans="15:18" x14ac:dyDescent="0.25">
@@ -3422,10 +3419,10 @@
         <v>8</v>
       </c>
       <c r="Q113">
-        <v>79.947634935599766</v>
+        <v>85.488721040356282</v>
       </c>
       <c r="R113">
-        <v>11.427190805917643</v>
+        <v>19.199648568189559</v>
       </c>
     </row>
     <row r="114" spans="15:18" x14ac:dyDescent="0.25">
@@ -3450,10 +3447,10 @@
         <v>8</v>
       </c>
       <c r="Q115">
-        <v>77.016592958785239</v>
+        <v>77.418385659092905</v>
       </c>
       <c r="R115">
-        <v>7.7966596562838326</v>
+        <v>7.3707188726535096</v>
       </c>
     </row>
     <row r="116" spans="15:18" x14ac:dyDescent="0.25">
@@ -3464,10 +3461,10 @@
         <v>8</v>
       </c>
       <c r="Q116">
-        <v>77.418385659092905</v>
+        <v>77.016592958785239</v>
       </c>
       <c r="R116">
-        <v>7.3707188726535096</v>
+        <v>7.7966596562838326</v>
       </c>
     </row>
     <row r="117" spans="15:18" x14ac:dyDescent="0.25">
@@ -3478,10 +3475,10 @@
         <v>8</v>
       </c>
       <c r="Q117">
-        <v>80.712625172486895</v>
+        <v>80.485970658506119</v>
       </c>
       <c r="R117">
-        <v>15.257020235184816</v>
+        <v>12.756467098170049</v>
       </c>
     </row>
     <row r="118" spans="15:18" x14ac:dyDescent="0.25">
@@ -3492,10 +3489,10 @@
         <v>8</v>
       </c>
       <c r="Q118">
-        <v>83.945608235027095</v>
+        <v>80.410720845682292</v>
       </c>
       <c r="R118">
-        <v>17.854854322167657</v>
+        <v>10.58438967691929</v>
       </c>
     </row>
     <row r="119" spans="15:18" x14ac:dyDescent="0.25">
@@ -3506,10 +3503,10 @@
         <v>8</v>
       </c>
       <c r="Q119">
-        <v>82.735576508982589</v>
+        <v>79.983076681947793</v>
       </c>
       <c r="R119">
-        <v>16.760193191518969</v>
+        <v>11.43036770345066</v>
       </c>
     </row>
     <row r="120" spans="15:18" x14ac:dyDescent="0.25">
@@ -3520,10 +3517,10 @@
         <v>8</v>
       </c>
       <c r="Q120">
-        <v>88.817161425025134</v>
+        <v>82.70745157151454</v>
       </c>
       <c r="R120">
-        <v>20.60369682782548</v>
+        <v>16.772624744207636</v>
       </c>
     </row>
     <row r="121" spans="15:18" x14ac:dyDescent="0.25">
@@ -3534,10 +3531,10 @@
         <v>8</v>
       </c>
       <c r="Q121">
-        <v>87.205281355072941</v>
+        <v>80.398912703831485</v>
       </c>
       <c r="R121">
-        <v>20.113583370257921</v>
+        <v>14.271648656886221</v>
       </c>
     </row>
     <row r="122" spans="15:18" x14ac:dyDescent="0.25">
@@ -3548,10 +3545,10 @@
         <v>8</v>
       </c>
       <c r="Q122">
-        <v>85.22771297280012</v>
+        <v>80.755419008527241</v>
       </c>
       <c r="R122">
-        <v>18.969725043879009</v>
+        <v>15.356907810679193</v>
       </c>
     </row>
     <row r="123" spans="15:18" x14ac:dyDescent="0.25">
@@ -3562,10 +3559,10 @@
         <v>8</v>
       </c>
       <c r="Q123">
-        <v>80.530279009447071</v>
+        <v>81.836685291033888</v>
       </c>
       <c r="R123">
-        <v>27.568646248158934</v>
+        <v>21.10302119312308</v>
       </c>
     </row>
     <row r="124" spans="15:18" x14ac:dyDescent="0.25">
@@ -3576,10 +3573,10 @@
         <v>8</v>
       </c>
       <c r="Q124">
-        <v>82.691638318475043</v>
+        <v>80.882423042649279</v>
       </c>
       <c r="R124">
-        <v>27.145978538045068</v>
+        <v>20.564145975997764</v>
       </c>
     </row>
     <row r="125" spans="15:18" x14ac:dyDescent="0.25">
@@ -3590,10 +3587,10 @@
         <v>8</v>
       </c>
       <c r="Q125">
-        <v>81.894536080706928</v>
+        <v>78.372555299819496</v>
       </c>
       <c r="R125">
-        <v>26.261782828491764</v>
+        <v>21.398204141725973</v>
       </c>
     </row>
     <row r="126" spans="15:18" x14ac:dyDescent="0.25">
@@ -3604,10 +3601,10 @@
         <v>8</v>
       </c>
       <c r="Q126">
-        <v>78.594686526388912</v>
+        <v>79.409394755798345</v>
       </c>
       <c r="R126">
-        <v>28.793343383966917</v>
+        <v>22.35706706178409</v>
       </c>
     </row>
     <row r="127" spans="15:18" x14ac:dyDescent="0.25">
@@ -3618,10 +3615,10 @@
         <v>8</v>
       </c>
       <c r="Q127">
-        <v>76.91112272158604</v>
+        <v>82.080754959948678</v>
       </c>
       <c r="R127">
-        <v>29.984016069110275</v>
+        <v>17.047156637410964</v>
       </c>
     </row>
     <row r="128" spans="15:18" x14ac:dyDescent="0.25">
@@ -3632,10 +3629,10 @@
         <v>8</v>
       </c>
       <c r="Q128">
-        <v>79.18419934082182</v>
+        <v>80.399560371503512</v>
       </c>
       <c r="R128">
-        <v>27.08812509039273</v>
+        <v>16.542337853473501</v>
       </c>
     </row>
     <row r="129" spans="15:18" x14ac:dyDescent="0.25">
@@ -3646,10 +3643,10 @@
         <v>8</v>
       </c>
       <c r="Q129">
-        <v>78.186541293088169</v>
+        <v>79.974506488817923</v>
       </c>
       <c r="R129">
-        <v>26.91880842422681</v>
+        <v>17.900431830287829</v>
       </c>
     </row>
     <row r="130" spans="15:18" x14ac:dyDescent="0.25">
@@ -3660,10 +3657,10 @@
         <v>8</v>
       </c>
       <c r="Q130">
-        <v>77.206378475969643</v>
+        <v>82.431444704649735</v>
       </c>
       <c r="R130">
-        <v>28.675336697419748</v>
+        <v>19.170938202533385</v>
       </c>
     </row>
     <row r="131" spans="15:18" x14ac:dyDescent="0.25">
@@ -3674,10 +3671,10 @@
         <v>8</v>
       </c>
       <c r="Q131">
-        <v>80.311440502453877</v>
+        <v>77.850993062754938</v>
       </c>
       <c r="R131">
-        <v>23.74652281159376</v>
+        <v>19.722675533708053</v>
       </c>
     </row>
     <row r="132" spans="15:18" x14ac:dyDescent="0.25">
@@ -3688,10 +3685,10 @@
         <v>8</v>
       </c>
       <c r="Q132">
-        <v>81.66199114710119</v>
+        <v>79.543664029918432</v>
       </c>
       <c r="R132">
-        <v>23.069873841603343</v>
+        <v>19.634603963339028</v>
       </c>
     </row>
     <row r="133" spans="15:18" x14ac:dyDescent="0.25">
@@ -3702,10 +3699,10 @@
         <v>8</v>
       </c>
       <c r="Q133">
-        <v>81.745172086474199</v>
+        <v>73.117191828301557</v>
       </c>
       <c r="R133">
-        <v>24.403260639081125</v>
+        <v>18.10188133634929</v>
       </c>
     </row>
     <row r="134" spans="15:18" x14ac:dyDescent="0.25">
@@ -3716,10 +3713,10 @@
         <v>8</v>
       </c>
       <c r="Q134">
-        <v>79.634886727627389</v>
+        <v>74.319190274631552</v>
       </c>
       <c r="R134">
-        <v>21.773659233214904</v>
+        <v>15.819154094000121</v>
       </c>
     </row>
     <row r="135" spans="15:18" x14ac:dyDescent="0.25">
@@ -3730,10 +3727,10 @@
         <v>8</v>
       </c>
       <c r="Q135">
-        <v>82.637600142585043</v>
+        <v>77.12049771033233</v>
       </c>
       <c r="R135">
-        <v>20.962799621758052</v>
+        <v>12.425595365564485</v>
       </c>
     </row>
     <row r="136" spans="15:18" x14ac:dyDescent="0.25">
@@ -3744,10 +3741,10 @@
         <v>8</v>
       </c>
       <c r="Q136">
-        <v>80.516222336466086</v>
+        <v>78.639677484304769</v>
       </c>
       <c r="R136">
-        <v>20.584886838633903</v>
+        <v>14.550177980339036</v>
       </c>
     </row>
     <row r="137" spans="15:18" x14ac:dyDescent="0.25">
@@ -3758,10 +3755,10 @@
         <v>8</v>
       </c>
       <c r="Q137">
-        <v>82.149176502195019</v>
+        <v>78.450493396292188</v>
       </c>
       <c r="R137">
-        <v>19.756636381724764</v>
+        <v>17.542829845456627</v>
       </c>
     </row>
     <row r="138" spans="15:18" x14ac:dyDescent="0.25">
@@ -3772,10 +3769,10 @@
         <v>8</v>
       </c>
       <c r="Q138">
-        <v>84.814362991919268</v>
+        <v>76.807084539797074</v>
       </c>
       <c r="R138">
-        <v>26.444177635438987</v>
+        <v>16.910107120094079</v>
       </c>
     </row>
     <row r="139" spans="15:18" x14ac:dyDescent="0.25">
@@ -3786,10 +3783,10 @@
         <v>8</v>
       </c>
       <c r="Q139">
-        <v>84.574649631813244</v>
+        <v>74.473661275825464</v>
       </c>
       <c r="R139">
-        <v>25.688543313501697</v>
+        <v>18.813105142821843</v>
       </c>
     </row>
     <row r="140" spans="15:18" x14ac:dyDescent="0.25">
@@ -3800,10 +3797,10 @@
         <v>8</v>
       </c>
       <c r="Q140">
-        <v>84.068049540960899</v>
+        <v>75.424040724855487</v>
       </c>
       <c r="R140">
-        <v>24.864264630017956</v>
+        <v>15.649766809815487</v>
       </c>
     </row>
     <row r="141" spans="15:18" x14ac:dyDescent="0.25">
@@ -3814,10 +3811,10 @@
         <v>8</v>
       </c>
       <c r="Q141">
-        <v>82.463672409316786</v>
+        <v>79.866875548815287</v>
       </c>
       <c r="R141">
-        <v>25.390120554977347</v>
+        <v>14.202095073903171</v>
       </c>
     </row>
     <row r="142" spans="15:18" x14ac:dyDescent="0.25">
@@ -3828,10 +3825,10 @@
         <v>8</v>
       </c>
       <c r="Q142">
-        <v>84.863533005125817</v>
+        <v>79.33897155145317</v>
       </c>
       <c r="R142">
-        <v>22.925991025423496</v>
+        <v>11.533505704106645</v>
       </c>
     </row>
     <row r="143" spans="15:18" x14ac:dyDescent="0.25">
@@ -3842,10 +3839,10 @@
         <v>8</v>
       </c>
       <c r="Q143">
-        <v>85.626078256446874</v>
+        <v>78.643107010547567</v>
       </c>
       <c r="R143">
-        <v>24.009329258537434</v>
+        <v>9.5960760827453928</v>
       </c>
     </row>
     <row r="144" spans="15:18" x14ac:dyDescent="0.25">
@@ -3856,10 +3853,10 @@
         <v>8</v>
       </c>
       <c r="Q144">
-        <v>91.364697610929326</v>
+        <v>77.440191307783152</v>
       </c>
       <c r="R144">
-        <v>23.434164569737867</v>
+        <v>8.7327490443746854</v>
       </c>
     </row>
     <row r="145" spans="15:18" x14ac:dyDescent="0.25">
@@ -3870,10 +3867,10 @@
         <v>8</v>
       </c>
       <c r="Q145">
-        <v>88.276459531453753</v>
+        <v>74.857241285934549</v>
       </c>
       <c r="R145">
-        <v>22.634024681322742</v>
+        <v>21.155816757932119</v>
       </c>
     </row>
     <row r="146" spans="15:18" x14ac:dyDescent="0.25">
@@ -3884,10 +3881,10 @@
         <v>8</v>
       </c>
       <c r="Q146">
-        <v>85.800052197183547</v>
+        <v>76.353024478012046</v>
       </c>
       <c r="R146">
-        <v>20.106235602515724</v>
+        <v>20.206900055993938</v>
       </c>
     </row>
     <row r="147" spans="15:18" x14ac:dyDescent="0.25">
@@ -3898,10 +3895,10 @@
         <v>8</v>
       </c>
       <c r="Q147">
-        <v>87.097363310443356</v>
+        <v>71.045609463613943</v>
       </c>
       <c r="R147">
-        <v>23.186798131460439</v>
+        <v>21.779166178569184</v>
       </c>
     </row>
     <row r="148" spans="15:18" x14ac:dyDescent="0.25">
@@ -3912,10 +3909,10 @@
         <v>8</v>
       </c>
       <c r="Q148">
-        <v>87.713139076831325</v>
+        <v>73.397808100437302</v>
       </c>
       <c r="R148">
-        <v>24.413894232513851</v>
+        <v>20.942569276881464</v>
       </c>
     </row>
     <row r="149" spans="15:18" x14ac:dyDescent="0.25">
@@ -3926,10 +3923,10 @@
         <v>8</v>
       </c>
       <c r="Q149">
-        <v>86.742517984861067</v>
+        <v>70.311592591472788</v>
       </c>
       <c r="R149">
-        <v>26.066552421403856</v>
+        <v>27.347823277046995</v>
       </c>
     </row>
     <row r="150" spans="15:18" x14ac:dyDescent="0.25">
@@ -3940,10 +3937,10 @@
         <v>8</v>
       </c>
       <c r="Q150">
-        <v>88.519468667917849</v>
+        <v>72.586998984902635</v>
       </c>
       <c r="R150">
-        <v>25.36439741125924</v>
+        <v>27.668212329370533</v>
       </c>
     </row>
     <row r="151" spans="15:18" x14ac:dyDescent="0.25">
@@ -3954,10 +3951,10 @@
         <v>8</v>
       </c>
       <c r="Q151">
-        <v>80.642825217012117</v>
+        <v>73.729865416877516</v>
       </c>
       <c r="R151">
-        <v>17.151776970611138</v>
+        <v>29.808688540741539</v>
       </c>
     </row>
     <row r="152" spans="15:18" x14ac:dyDescent="0.25">
@@ -3968,10 +3965,10 @@
         <v>8</v>
       </c>
       <c r="Q152">
-        <v>80.309702751630525</v>
+        <v>73.916253181524226</v>
       </c>
       <c r="R152">
-        <v>15.731577817652772</v>
+        <v>28.54206364942322</v>
       </c>
     </row>
     <row r="153" spans="15:18" x14ac:dyDescent="0.25">
@@ -3982,10 +3979,10 @@
         <v>8</v>
       </c>
       <c r="Q153">
-        <v>79.347299662889384</v>
+        <v>71.642393294309116</v>
       </c>
       <c r="R153">
-        <v>19.307871111566858</v>
+        <v>25.844148868044844</v>
       </c>
     </row>
     <row r="154" spans="15:18" x14ac:dyDescent="0.25">
@@ -3996,10 +3993,10 @@
         <v>8</v>
       </c>
       <c r="Q154">
-        <v>82.35220938638534</v>
+        <v>69.491584547532014</v>
       </c>
       <c r="R154">
-        <v>18.434863476578929</v>
+        <v>23.537382204563563</v>
       </c>
     </row>
     <row r="155" spans="15:18" x14ac:dyDescent="0.25">
@@ -4010,10 +4007,10 @@
         <v>8</v>
       </c>
       <c r="Q155">
-        <v>78.057322734683396</v>
+        <v>71.219253161407536</v>
       </c>
       <c r="R155">
-        <v>20.873713797988938</v>
+        <v>23.867012447458531</v>
       </c>
     </row>
     <row r="156" spans="15:18" x14ac:dyDescent="0.25">
@@ -4024,10 +4021,10 @@
         <v>8</v>
       </c>
       <c r="Q156">
-        <v>74.415531049013609</v>
+        <v>72.89178314089699</v>
       </c>
       <c r="R156">
-        <v>19.257126862183384</v>
+        <v>23.161319960013007</v>
       </c>
     </row>
     <row r="157" spans="15:18" x14ac:dyDescent="0.25">
@@ -4038,10 +4035,10 @@
         <v>8</v>
       </c>
       <c r="Q157">
-        <v>75.788587835847693</v>
+        <v>74.316530316007331</v>
       </c>
       <c r="R157">
-        <v>20.86372113464547</v>
+        <v>23.62601404726578</v>
       </c>
     </row>
     <row r="158" spans="15:18" x14ac:dyDescent="0.25">
@@ -4052,10 +4049,10 @@
         <v>8</v>
       </c>
       <c r="Q158">
-        <v>78.643107010547567</v>
+        <v>77.120257706706013</v>
       </c>
       <c r="R158">
-        <v>9.5960760827453928</v>
+        <v>22.764211806411765</v>
       </c>
     </row>
     <row r="159" spans="15:18" x14ac:dyDescent="0.25">
@@ -4066,10 +4063,10 @@
         <v>8</v>
       </c>
       <c r="Q159">
-        <v>79.433368253396324</v>
+        <v>76.570584902688594</v>
       </c>
       <c r="R159">
-        <v>11.888456297244469</v>
+        <v>24.020412520611149</v>
       </c>
     </row>
     <row r="160" spans="15:18" x14ac:dyDescent="0.25">
@@ -4080,10 +4077,10 @@
         <v>8</v>
       </c>
       <c r="Q160">
-        <v>79.105957638268393</v>
+        <v>74.764996798480269</v>
       </c>
       <c r="R160">
-        <v>15.200429542357904</v>
+        <v>25.841336832412249</v>
       </c>
     </row>
     <row r="161" spans="15:18" x14ac:dyDescent="0.25">
@@ -4094,10 +4091,10 @@
         <v>8</v>
       </c>
       <c r="Q161">
-        <v>78.703731334785473</v>
+        <v>75.718103311208239</v>
       </c>
       <c r="R161">
-        <v>12.277183904189595</v>
+        <v>26.705063158497371</v>
       </c>
     </row>
     <row r="162" spans="15:18" x14ac:dyDescent="0.25">
@@ -4108,10 +4105,10 @@
         <v>8</v>
       </c>
       <c r="Q162">
-        <v>78.158973175470464</v>
+        <v>85.744169475346055</v>
       </c>
       <c r="R162">
-        <v>17.97193329665479</v>
+        <v>19.778519454413203</v>
       </c>
     </row>
     <row r="163" spans="15:18" x14ac:dyDescent="0.25">
@@ -4122,10 +4119,10 @@
         <v>8</v>
       </c>
       <c r="Q163">
-        <v>76.392431566147351</v>
+        <v>91.364697610929326</v>
       </c>
       <c r="R163">
-        <v>17.301133896012278</v>
+        <v>23.434164569737867</v>
       </c>
     </row>
     <row r="164" spans="15:18" x14ac:dyDescent="0.25">
@@ -4136,10 +4133,10 @@
         <v>8</v>
       </c>
       <c r="Q164">
-        <v>77.687512372796817</v>
+        <v>88.021741728573033</v>
       </c>
       <c r="R164">
-        <v>14.689600757873064</v>
+        <v>23.416858734520115</v>
       </c>
     </row>
     <row r="165" spans="15:18" x14ac:dyDescent="0.25">
@@ -4150,10 +4147,10 @@
         <v>8</v>
       </c>
       <c r="Q165">
-        <v>73.117191828301557</v>
+        <v>88.017609000282519</v>
       </c>
       <c r="R165">
-        <v>18.10188133634929</v>
+        <v>22.250500124823297</v>
       </c>
     </row>
     <row r="166" spans="15:18" x14ac:dyDescent="0.25">
@@ -4164,10 +4161,10 @@
         <v>8</v>
       </c>
       <c r="Q166">
-        <v>74.044050798041852</v>
+        <v>88.092629835435545</v>
       </c>
       <c r="R166">
-        <v>16.397943140481793</v>
+        <v>24.930627855967352</v>
       </c>
     </row>
     <row r="167" spans="15:18" x14ac:dyDescent="0.25">
@@ -4178,10 +4175,10 @@
         <v>8</v>
       </c>
       <c r="Q167">
-        <v>77.332804703750128</v>
+        <v>87.933042646001581</v>
       </c>
       <c r="R167">
-        <v>10.027937903487528</v>
+        <v>25.981759940260336</v>
       </c>
     </row>
     <row r="168" spans="15:18" x14ac:dyDescent="0.25">
@@ -4192,10 +4189,10 @@
         <v>8</v>
       </c>
       <c r="Q168">
-        <v>76.610684968333302</v>
+        <v>86.731586168708432</v>
       </c>
       <c r="R168">
-        <v>12.845887555989639</v>
+        <v>24.438742310878997</v>
       </c>
     </row>
     <row r="169" spans="15:18" x14ac:dyDescent="0.25">
@@ -4206,10 +4203,10 @@
         <v>8</v>
       </c>
       <c r="Q169">
-        <v>75.329007834456249</v>
+        <v>85.648859894094272</v>
       </c>
       <c r="R169">
-        <v>15.430546310682852</v>
+        <v>23.739395610876532</v>
       </c>
     </row>
     <row r="170" spans="15:18" x14ac:dyDescent="0.25">
@@ -4220,10 +4217,10 @@
         <v>8</v>
       </c>
       <c r="Q170">
-        <v>69.837381407326902</v>
+        <v>77.206378475969643</v>
       </c>
       <c r="R170">
-        <v>23.641546613525119</v>
+        <v>28.675336697419748</v>
       </c>
     </row>
     <row r="171" spans="15:18" x14ac:dyDescent="0.25">
@@ -4234,10 +4231,10 @@
         <v>8</v>
       </c>
       <c r="Q171">
-        <v>73.337752020795662</v>
+        <v>77.108470507158842</v>
       </c>
       <c r="R171">
-        <v>20.235293020913748</v>
+        <v>29.785580394435748</v>
       </c>
     </row>
     <row r="172" spans="15:18" x14ac:dyDescent="0.25">
@@ -4248,10 +4245,10 @@
         <v>8</v>
       </c>
       <c r="Q172">
-        <v>71.910307761551564</v>
+        <v>78.854484297853048</v>
       </c>
       <c r="R172">
-        <v>21.79451137025972</v>
+        <v>28.674684289117295</v>
       </c>
     </row>
     <row r="173" spans="15:18" x14ac:dyDescent="0.25">
@@ -4262,10 +4259,10 @@
         <v>8</v>
       </c>
       <c r="Q173">
-        <v>73.378772638489167</v>
+        <v>78.778863095358872</v>
       </c>
       <c r="R173">
-        <v>23.332530133704456</v>
+        <v>27.472156910090767</v>
       </c>
     </row>
     <row r="174" spans="15:18" x14ac:dyDescent="0.25">
@@ -4276,10 +4273,10 @@
         <v>8</v>
       </c>
       <c r="Q174">
-        <v>72.547991113350264</v>
+        <v>75.491066578156577</v>
       </c>
       <c r="R174">
-        <v>26.235298616044037</v>
+        <v>29.758564095811749</v>
       </c>
     </row>
     <row r="175" spans="15:18" x14ac:dyDescent="0.25">
@@ -4290,10 +4287,10 @@
         <v>8</v>
       </c>
       <c r="Q175">
-        <v>72.376138727460813</v>
+        <v>77.401966664144197</v>
       </c>
       <c r="R175">
-        <v>24.684505937472583</v>
+        <v>26.88906112537213</v>
       </c>
     </row>
     <row r="176" spans="15:18" x14ac:dyDescent="0.25">
@@ -4304,10 +4301,10 @@
         <v>8</v>
       </c>
       <c r="Q176">
-        <v>78.857355389286042</v>
+        <v>75.709283316468529</v>
       </c>
       <c r="R176">
-        <v>23.13865428301451</v>
+        <v>28.293682817624759</v>
       </c>
     </row>
     <row r="177" spans="15:18" x14ac:dyDescent="0.25">
@@ -4318,10 +4315,10 @@
         <v>8</v>
       </c>
       <c r="Q177">
-        <v>75.952051871277561</v>
+        <v>85.86600946430508</v>
       </c>
       <c r="R177">
-        <v>22.820378648545816</v>
+        <v>25.877907701141385</v>
       </c>
     </row>
     <row r="178" spans="15:18" x14ac:dyDescent="0.25">
@@ -4332,10 +4329,10 @@
         <v>8</v>
       </c>
       <c r="Q178">
-        <v>76.306615158292246</v>
+        <v>83.507576624075199</v>
       </c>
       <c r="R178">
-        <v>24.161220077291691</v>
+        <v>26.705763894083677</v>
       </c>
     </row>
     <row r="179" spans="15:18" x14ac:dyDescent="0.25">
@@ -4346,10 +4343,10 @@
         <v>8</v>
       </c>
       <c r="Q179">
-        <v>74.760560472840439</v>
+        <v>80.716751371122385</v>
       </c>
       <c r="R179">
-        <v>25.796100801082744</v>
+        <v>27.480738799678608</v>
       </c>
     </row>
     <row r="180" spans="15:18" x14ac:dyDescent="0.25">
@@ -4360,10 +4357,10 @@
         <v>8</v>
       </c>
       <c r="Q180">
-        <v>76.349824832698488</v>
+        <v>84.101883963290859</v>
       </c>
       <c r="R180">
-        <v>26.049462668053657</v>
+        <v>25.254802896666462</v>
       </c>
     </row>
     <row r="181" spans="15:18" x14ac:dyDescent="0.25">
@@ -4374,10 +4371,10 @@
         <v>8</v>
       </c>
       <c r="Q181">
-        <v>79.539005682974107</v>
+        <v>80.552528139644522</v>
       </c>
       <c r="R181">
-        <v>25.61450482481651</v>
+        <v>26.316112387828863</v>
       </c>
     </row>
     <row r="182" spans="15:18" x14ac:dyDescent="0.25">
@@ -4388,10 +4385,10 @@
         <v>8</v>
       </c>
       <c r="Q182">
-        <v>78.328118769062314</v>
+        <v>82.184691273926532</v>
       </c>
       <c r="R182">
-        <v>25.026982238537776</v>
+        <v>25.865693876057371</v>
       </c>
     </row>
     <row r="183" spans="15:18" x14ac:dyDescent="0.25">
@@ -4402,10 +4399,10 @@
         <v>8</v>
       </c>
       <c r="Q183">
-        <v>75.419785716757175</v>
+        <v>81.993704388759994</v>
       </c>
       <c r="R183">
-        <v>29.938128170820484</v>
+        <v>24.557967234305494</v>
       </c>
     </row>
     <row r="184" spans="15:18" x14ac:dyDescent="0.25">
@@ -4416,10 +4413,10 @@
         <v>8</v>
       </c>
       <c r="Q184">
-        <v>76.848824901998555</v>
+        <v>80.207230676793614</v>
       </c>
       <c r="R184">
-        <v>27.120371663022347</v>
+        <v>24.206899938274063</v>
       </c>
     </row>
     <row r="185" spans="15:18" x14ac:dyDescent="0.25">
@@ -4430,10 +4427,10 @@
         <v>8</v>
       </c>
       <c r="Q185">
-        <v>75.693889534677325</v>
+        <v>80.651317068900511</v>
       </c>
       <c r="R185">
-        <v>28.744986231599484</v>
+        <v>23.218073818817498</v>
       </c>
     </row>
     <row r="186" spans="15:18" x14ac:dyDescent="0.25">
@@ -4444,10 +4441,10 @@
         <v>8</v>
       </c>
       <c r="Q186">
-        <v>70.583748235256252</v>
+        <v>79.392354876609716</v>
       </c>
       <c r="R186">
-        <v>27.17014391183822</v>
+        <v>25.913846570056801</v>
       </c>
     </row>
     <row r="187" spans="15:18" x14ac:dyDescent="0.25">
@@ -4458,10 +4455,10 @@
         <v>8</v>
       </c>
       <c r="Q187">
-        <v>73.398080587990734</v>
+        <v>78.127315494079511</v>
       </c>
       <c r="R187">
-        <v>29.159276273167201</v>
+        <v>25.658891382800981</v>
       </c>
     </row>
     <row r="188" spans="15:18" x14ac:dyDescent="0.25">
@@ -4472,24 +4469,10 @@
         <v>8</v>
       </c>
       <c r="Q188">
-        <v>75.125044446248808</v>
+        <v>78.675749297627448</v>
       </c>
       <c r="R188">
-        <v>27.65927345946567</v>
-      </c>
-    </row>
-    <row r="189" spans="15:18" x14ac:dyDescent="0.25">
-      <c r="O189" t="s">
-        <v>253</v>
-      </c>
-      <c r="P189" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q189">
-        <v>73.375033041660885</v>
-      </c>
-      <c r="R189">
-        <v>27.582754040290936</v>
+        <v>24.298768402411401</v>
       </c>
     </row>
   </sheetData>
